--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.62540056893346</v>
+        <v>6.764127592451687</v>
       </c>
       <c r="D2" t="n">
-        <v>40.42902662971563</v>
+        <v>6.56971682732879</v>
       </c>
       <c r="E2" t="n">
-        <v>17.04060166421857</v>
+        <v>2.769097770435517</v>
       </c>
       <c r="F2" t="n">
-        <v>25.03424785335911</v>
+        <v>4.068065276170855</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>64.68434204733465</v>
+        <v>10.51120558269188</v>
       </c>
       <c r="D3" t="n">
-        <v>63.88241683039818</v>
+        <v>10.3808927349397</v>
       </c>
       <c r="E3" t="n">
-        <v>17.04060166421857</v>
+        <v>2.769097770435517</v>
       </c>
       <c r="F3" t="n">
-        <v>25.03424785335911</v>
+        <v>4.068065276170855</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>94.95401305109283</v>
+        <v>15.43002712080258</v>
       </c>
       <c r="D4" t="n">
-        <v>95.50055789854241</v>
+        <v>15.51884065851314</v>
       </c>
       <c r="E4" t="n">
-        <v>17.04060166421857</v>
+        <v>2.769097770435517</v>
       </c>
       <c r="F4" t="n">
-        <v>25.03424785335911</v>
+        <v>4.068065276170855</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>72.56811947318282</v>
+        <v>11.79231941439221</v>
       </c>
       <c r="D5" t="n">
-        <v>73.40056477426138</v>
+        <v>11.92759177581748</v>
       </c>
       <c r="E5" t="n">
-        <v>17.04060166421857</v>
+        <v>2.769097770435517</v>
       </c>
       <c r="F5" t="n">
-        <v>25.03424785335911</v>
+        <v>4.068065276170855</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>63.2159755961931</v>
+        <v>10.27259603438138</v>
       </c>
       <c r="D6" t="n">
-        <v>64.01319517013003</v>
+        <v>10.40214421514613</v>
       </c>
       <c r="E6" t="n">
-        <v>17.04060166421857</v>
+        <v>2.769097770435517</v>
       </c>
       <c r="F6" t="n">
-        <v>25.03424785335911</v>
+        <v>4.068065276170855</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.29195739615379</v>
+        <v>5.572443076874992</v>
       </c>
       <c r="D7" t="n">
-        <v>6.508541396588879</v>
+        <v>1.057637976945693</v>
       </c>
       <c r="E7" t="n">
-        <v>17.04060166421857</v>
+        <v>2.769097770435517</v>
       </c>
       <c r="F7" t="n">
-        <v>25.03424785335911</v>
+        <v>4.068065276170855</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.98308275234512</v>
+        <v>6.497250947256082</v>
       </c>
       <c r="D8" t="n">
-        <v>15.8113883008419</v>
+        <v>2.569350598886808</v>
       </c>
       <c r="E8" t="n">
-        <v>17.04060166421857</v>
+        <v>2.769097770435517</v>
       </c>
       <c r="F8" t="n">
-        <v>25.03424785335911</v>
+        <v>4.068065276170855</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>62.09189451364998</v>
+        <v>10.08993285846812</v>
       </c>
       <c r="D9" t="n">
-        <v>44.95427580976303</v>
+        <v>7.305069819086493</v>
       </c>
       <c r="E9" t="n">
-        <v>17.04060166421857</v>
+        <v>2.769097770435517</v>
       </c>
       <c r="F9" t="n">
-        <v>25.03424785335911</v>
+        <v>4.068065276170855</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>49.24714813052287</v>
+        <v>8.002661571209968</v>
       </c>
       <c r="D10" t="n">
-        <v>48.95807080751054</v>
+        <v>7.955686506220464</v>
       </c>
       <c r="E10" t="n">
-        <v>17.04060166421857</v>
+        <v>2.769097770435517</v>
       </c>
       <c r="F10" t="n">
-        <v>25.03424785335911</v>
+        <v>4.068065276170855</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>60.65329942665837</v>
+        <v>9.856161156831986</v>
       </c>
       <c r="D11" t="n">
-        <v>59.98569427325735</v>
+        <v>9.747675319404319</v>
       </c>
       <c r="E11" t="n">
-        <v>17.04060166421857</v>
+        <v>2.769097770435517</v>
       </c>
       <c r="F11" t="n">
-        <v>25.03424785335911</v>
+        <v>4.068065276170855</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
